--- a/public/resume-data.xlsx
+++ b/public/resume-data.xlsx
@@ -92,7 +92,7 @@
     <t xml:space="preserve">Introduction</t>
   </si>
   <si>
-    <t xml:space="preserve">Frontend/UI engineering leader with 17+ years of software development experience, including 8+ years at Flipkart architecting customer-facing web and mobile commerce experiences for a customer base that scaled from roughly 100 million to 500 million+ registered users. Deep expertise across React, React Native, TypeScript, JavaScript, and Node.js, with a specialization in payments UI — having shipped 8+ payment instruments, including India’s first no-cost EMI checkout, UPI, Buy-Now-Pay-Later, and a co-branded credit card that scaled past 3 million cards issued. Proven track record leading end-to-end delivery, driving UI modernization, mentoring 10+ engineers, and ensuring production reliability (99.99% uptime) through canary deployments — including payments UI technology readiness across 8 consecutive editions of Flipkart’s flagship Big Billion Days sale.</t>
+    <t xml:space="preserve">Frontend/UI engineering leader with 16+ years of software development experience, including 8+ years at Flipkart architecting customer-facing web and mobile commerce experiences for a customer base that scaled from roughly 100 million to 500 million+ registered users. Deep expertise across React, React Native, TypeScript, JavaScript, and Node.js, with a specialization in payments UI — having shipped 8+ payment instruments, including India’s first no-cost EMI checkout, UPI, Buy-Now-Pay-Later, and a co-branded credit card that scaled past 3 million cards issued. Proven track record leading end-to-end delivery, driving UI modernization, mentoring 10+ engineers, and ensuring production reliability (99.99% uptime) through canary deployments — including payments UI technology readiness across 8 consecutive editions of Flipkart’s flagship Big Billion Days sale.</t>
   </si>
   <si>
     <t xml:space="preserve">Address</t>
